--- a/artfynd/S 929-2023 artfynd.xlsx
+++ b/artfynd/S 929-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,32 +1268,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93625897</v>
+        <v>136661116</v>
       </c>
       <c r="B7" t="n">
-        <v>57942</v>
+        <v>9417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102119</v>
+        <v>101246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1301,26 +1301,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Frögården, Öl</t>
+          <t>Stora Frögårdsvägen 30, Öl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586473</v>
+        <v>586306</v>
       </c>
       <c r="R7" t="n">
-        <v>6271019</v>
+        <v>6271068</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,12 +1342,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Död hane</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,44 +1377,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Karlsson</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Karlsson</t>
+          <t>Via Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93625897</t>
+          <t>https://artportalen.se/Sighting/136661116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117439976</v>
+        <v>93625897</v>
       </c>
       <c r="B8" t="n">
-        <v>58353</v>
+        <v>57942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103037</v>
+        <v>102119</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1411,34 +1424,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Haga park, Öl</t>
+          <t>Stora Frögården, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586583</v>
+        <v>586473</v>
       </c>
       <c r="R8" t="n">
-        <v>6271107</v>
+        <v>6271019</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,12 +1470,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,44 +1490,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Magnus Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Magnus Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117439976</t>
+          <t>https://artportalen.se/Sighting/93625897</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102293148</v>
+        <v>117439976</v>
       </c>
       <c r="B9" t="n">
-        <v>56876</v>
+        <v>58353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208257</v>
+        <v>103037</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1529,31 +1537,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Haga Park, Öl</t>
+          <t>Haga park, Öl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586721</v>
+        <v>586583</v>
       </c>
       <c r="R9" t="n">
-        <v>6271048</v>
+        <v>6271107</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,12 +1588,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,34 +1602,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Lysell</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Lysell</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102293148</t>
+          <t>https://artportalen.se/Sighting/117439976</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2151770</v>
+        <v>102293148</v>
       </c>
       <c r="B10" t="n">
-        <v>111175</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1636,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>208257</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Frö, Öl</t>
+          <t>Haga Park, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586650</v>
+        <v>586721</v>
       </c>
       <c r="R10" t="n">
-        <v>6270956</v>
+        <v>6271048</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,12 +1703,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2008-02-23</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2008-02-23</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,84 +1717,72 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Fredrik Lysell</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Fredrik Lysell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2151770</t>
+          <t>https://artportalen.se/Sighting/102293148</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78401551</v>
+        <v>2151770</v>
       </c>
       <c r="B11" t="n">
-        <v>99754</v>
+        <v>111175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222295</v>
+        <v>219677</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Frö V, Öl</t>
+          <t>Stora Frö, Öl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586706</v>
+        <v>586650</v>
       </c>
       <c r="R11" t="n">
-        <v>6271063</v>
+        <v>6270956</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,12 +1806,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
+          <t>2008-02-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
+          <t>2008-02-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,19 +1820,23 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Waldenström</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Waldenström</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1831,54 +1846,58 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78401551</t>
+          <t>https://artportalen.se/Sighting/2151770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126770058</v>
+        <v>78401551</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>99754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037591</v>
+        <v>222295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten jordstjärna</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum granulosum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fuckel</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stora Frögården,infarten, Stora Frögården,infarten, Öl</t>
+          <t>Stora Frö V, Öl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586724</v>
+        <v>586706</v>
       </c>
       <c r="R12" t="n">
-        <v>6271082</v>
+        <v>6271063</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,22 +1921,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1935,139 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78401551</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126770058</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6037591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Liten jordstjärna</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Geastrum granulosum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Fuckel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stora Frögården,infarten, Stora Frögården,infarten, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>586724</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6271082</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vickleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Ingela Carlström</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126770058</t>
         </is>
@@ -1960,6 +2086,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 929-2023 artfynd.xlsx
+++ b/artfynd/S 929-2023 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>136661116</v>
       </c>
       <c r="B7" t="n">
-        <v>9417</v>
+        <v>9418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
